--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_372_Ireland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_372_Ireland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rbef85092b61341b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4be0c119663f41d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd9fbcf1625244de2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1a258384e83b467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2d09c1a81d334891"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9c839ca57ad14ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R90998c4876054571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Raca76fcbfb9945e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcf391353c48f4fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R907a45f829224177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb64365269de94dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R688c23f6019f4cfe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ372CommercialTable" displayName="EEZ372CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ372CommercialTable" displayName="EEZ372CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ372FunctionalTable" displayName="EEZ372FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ372FunctionalTable" displayName="EEZ372FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ372ValidationTable" displayName="EEZ372ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ372ValidationTable" displayName="EEZ372ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -19923,7 +19877,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd1c1ec743fb4415"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce3fe998b66443b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19933,20 +19887,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -19954,714 +19898,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1717.8549674249</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1717.8549674249</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$288,A2,'Species'!$U$2:$U$288))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>221302.589165895</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>221302.589165895</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>251602.6725653101</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.1517176262225535</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1418.1351650607432</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>251602.6725653101</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1454.0698539380544</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$288,A3,'Species'!$U$2:$U$288))</x:f>
-        <x:v>365847861.34746456</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.1517176262225535</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1418.1351650607432</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>356806597.5881302</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>9041263.759334385</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0253393962456123</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.025339396245612357</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>12500.8289831374</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.025321300796759</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>106.00376747929191</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>12500.8289831374</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>121.25071851882502</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$288,A4,'Species'!$U$2:$U$288))</x:f>
-        <x:v>1515734.4962863626</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.025321300796759</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>106.00376747929191</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1325134.9688268902</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>190599.52745947242</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1438340485635252</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.14383404856352522</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>9382.1305347819</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.65606089102774</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>452.96108366341963</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>9382.1305347819</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>622.1275667560112</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$288,A5,'Species'!$U$2:$U$288))</x:f>
-        <x:v>5836882.0405911375</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.65606089102774</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>452.96108366341963</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4249740.014106468</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1587142.0264846692</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3734680289185583</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3734680289185584</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>11323.4216677729</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0437664458216416</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>110.60288256356772</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>11323.4216677729</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.33214845940932</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$288,A6,'Species'!$U$2:$U$288))</x:f>
-        <x:v>1294631.1271883035</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0437664458216416</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>110.60288256356772</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1252403.0769384443</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>42228.050249859225</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0337176193730597</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.033717619373059664</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2486.5680279635</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.3531061060995753</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>22.547900313816143</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2486.5680279635</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>95.06538106821608</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$288,A7,'Species'!$U$2:$U$288))</x:f>
-        <x:v>236386.5371303927</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.3531061060995753</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>22.547900313816143</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>56066.888018043384</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>180319.64911234932</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>4.216152268952738</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>3.216152268952738</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>25971.452655648503</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9768429212550545</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>948.0754945321712</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>25971.452655648503</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1730.3334554455034</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$288,A8,'Species'!$U$2:$U$288))</x:f>
-        <x:v>44939273.41658757</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9768429212550545</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>948.0754945321712</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>24622897.820222825</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>20316375.596364744</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8251009180438085</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8251009180438085</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>85226.94465591351</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6415166448814156</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>438.04289939286673</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>85226.94465591351</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>455.54557687251776</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$288,A9,'Species'!$U$2:$U$288))</x:f>
-        <x:v>38824757.66836026</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6415166448814156</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>438.04289939286673</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>37333057.943471745</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1491699.7248885185</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0399565373709057</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.03995653737090575</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2279.5437353121</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3883436068909916</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>244.53645210706856</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2279.5437353121</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>252.9079449832412</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$288,A10,'Species'!$U$2:$U$288))</x:f>
-        <x:v>576514.7215972048</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3883436068909916</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>244.53645210706856</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>557431.5374561155</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>19083.184141089325</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0342341307565357</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03423413075653559</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>963.9724882360999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.718150957548782</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>522.5778016112396</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>963.9724882360999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>549.5954548032687</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$288,A11,'Species'!$U$2:$U$288))</x:f>
-        <x:v>529794.8980899579</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.718150957548782</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>522.5778016112396</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>503750.6237161376</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>26044.274373820284</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0517007287885685</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.05170072878856856</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4567.0074585643</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.044790752008099</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1108.6405310175214</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4567.0074585643</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1247.3616405939583</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$288,A12,'Species'!$U$2:$U$288))</x:f>
-        <x:v>5696709.916119609</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.044790752008099</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1108.6405310175214</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>5063169.574023706</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>633540.3420959031</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1251272217597144</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.12512722175971444</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>342.06419373690005</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.367286272200565</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2329.6263623923146</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>342.06419373690005</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2404.1048119036113</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$288,A13,'Species'!$U$2:$U$288))</x:f>
-        <x:v>822358.1741428106</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.367286272200565</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2329.6263623923146</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>796881.7633599545</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>25476.41078285617</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0319701265033825</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.031970126503382386</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce1780aec20f4176"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5b1484df74448dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20671,20 +20151,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -20692,1470 +20162,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1272.3162126011</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9186366359846616</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>829.1567412030172</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1272.3162126011</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>881.6288033293952</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$288,A2,'Species'!$U$2:$U$288))</x:f>
-        <x:v>1121710.619972096</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9186366359846616</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>829.1567412030172</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1054949.5646200932</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>66761.05535200285</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.063283646527732</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0632836465277321</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>684.5842992121</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.297429379633276</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1983.487096957538</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>684.5842992121</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2108.9309768579997</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$288,A3,'Species'!$U$2:$U$288))</x:f>
-        <x:v>1443741.0348790232</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.297429379633276</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1983.487096957538</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1357864.1242669187</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>85876.91061210446</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0632441118940876</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06324411189408774</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>174.0488060371</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.546049809350692</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>351.60076340185566</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>174.0488060371</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>360.57860626046585</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$288,A4,'Species'!$U$2:$U$288))</x:f>
-        <x:v>62758.27590215567</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.546049809350692</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>351.60076340185566</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>61195.693071825866</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1562.582830329804</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.025534196148343</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.025534196148343125</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2783.1395032187</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.0805205828368445</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1203.7064365811875</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2783.1395032187</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1250.7491085157765</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$288,A5,'Species'!$U$2:$U$288))</x:f>
-        <x:v>3481009.25252583</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.0805205828368445</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1203.7064365811875</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3350082.933927718</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>130926.31859811209</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0390815156461248</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.03908151564612489</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>20740.3700787023</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.411523617413235</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2579.429232821945</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>20740.3700787023</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2593.224175399549</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$288,A6,'Species'!$U$2:$U$288))</x:f>
-        <x:v>53784429.094824255</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.411523617413235</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2579.429232821945</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>53498316.880550295</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>286112.2142739594</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0053480601065037</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0053480601065036045</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1323.8484386341</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3398803717993264</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>218.71590790056456</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1323.8484386341</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>334.8845818127442</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$288,A7,'Species'!$U$2:$U$288))</x:f>
-        <x:v>443336.4307554349</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3398803717993264</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>218.71590790056456</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>289546.713178602</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>153789.71757683292</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5311395729157193</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5311395729157192</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>241.74343947050002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.338727452634661</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2181.3605399475905</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>241.74343947050002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2225.5185740807506</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$288,A8,'Species'!$U$2:$U$288))</x:f>
-        <x:v>538004.5147037634</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.338727452634661</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2181.3605399475905</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>527329.5996521576</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>10674.915051605785</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0202433450704214</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.02024334507042138</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>814.2304730817001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.807934700731235</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>642.5910919052999</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>814.2304730817001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>674.4465062978014</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$288,A9,'Species'!$U$2:$U$288))</x:f>
-        <x:v>549154.8978911587</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.807934700731235</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>642.5910919052999</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>523217.2487601386</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>25937.649131020124</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.049573383126195</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.049573383126195185</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>89.291781485</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.837769910198326</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>688.2875440614505</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>89.291781485</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>693.870664441444</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$288,A10,'Species'!$U$2:$U$288))</x:f>
-        <x:v>61956.947748157174</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.837769910198326</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>688.2875440614505</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>61458.42098318235</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>498.52676497482753</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0081116103700622</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.008111610370062156</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2424.6806314442997</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.196730795756785</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1573.0075088376955</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2424.6806314442997</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1634.3030473620672</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$288,A11,'Species'!$U$2:$U$288))</x:f>
-        <x:v>3962662.9448492005</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.196730795756785</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1573.0075088376955</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3814040.839795208</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>148622.10505399248</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0389670984912611</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.038967098491261204</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>11447.1833159505</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.0419737443236894</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>110.14727169722377</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>11447.1833159505</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>124.9555903759929</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$288,A12,'Species'!$U$2:$U$288))</x:f>
-        <x:v>1430389.5493868107</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.0419737443236894</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>110.14727169722377</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1260876.0108699268</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>169513.53851688397</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1344410846550488</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.13444108465504873</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>15847.4868907745</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.308884430509074</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2036.5000754356638</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>15847.4868907745</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2517.6500019293867</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$288,A13,'Species'!$U$2:$U$288))</x:f>
-        <x:v>39898425.40113435</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.308884430509074</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2036.5000754356638</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>32273408.248527963</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>7625017.152606387</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2362631518149056</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.23626315181490554</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>240.4897646027</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.049579602283844</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1120.9328642502462</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>240.4897646027</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1143.300130801285</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$288,A14,'Species'!$U$2:$U$288))</x:f>
-        <x:v>274951.9793266371</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.049579602283844</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1120.9328642502462</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>269572.880658972</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5379.098667665094</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0199541536022314</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.019954153602231295</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>221592.14915459498</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.133689215791421</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1360.4707715145853</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>221592.14915459498</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1366.2979630058792</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$288,A15,'Species'!$U$2:$U$288))</x:f>
-        <x:v>302760902.0080181</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.133689215791421</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1360.4707715145853</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>301469642.1219269</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1291259.8860911727</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0042832169667317</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.004283216966731706</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>18606.2477862524</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.557593162434791</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>361.0714603191899</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>18606.2477862524</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>515.4135662148087</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$288,A16,'Species'!$U$2:$U$288))</x:f>
-        <x:v>9589912.52538874</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.557593162434791</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>361.0714603191899</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>6718185.059242848</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2871727.4661458917</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.427455844223133</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.42745584422313315</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>82972.7208677585</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6556458985441145</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>452.52846093612754</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>82972.7208677585</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>462.99601119579876</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$288,A17,'Species'!$U$2:$U$288))</x:f>
-        <x:v>38416038.7998346</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6556458985441145</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>452.52846093612754</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>37547517.67396966</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>868521.1258649379</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0231312528675378</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.023131252867537824</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>220.14136632959998</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2889489290356617</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>194.5131329985017</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>220.14136632959998</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>217.58467749410397</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$288,A18,'Species'!$U$2:$U$288))</x:f>
-        <x:v>47899.38819593741</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2889489290356617</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>194.5131329985017</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>42820.38686734137</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>5079.001328596045</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.1186117571597594</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.1186117571597594</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2503.6001007973</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.3527544149915283</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>22.52964844456023</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2503.6001007973</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>94.55492324564882</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$288,A19,'Species'!$U$2:$U$288))</x:f>
-        <x:v>236727.71536868735</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.3527544149915283</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>22.52964844456023</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>56405.23011672872</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>180322.48525195863</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>4.196910727583015</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>3.1969107275830155</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1053.6456671869</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.8444031993440797</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>69.88809446053214</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1053.6456671869</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>80.999665786518</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$288,A20,'Species'!$U$2:$U$288))</x:f>
-        <x:v>85344.94689955167</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.8444031993440797</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>69.88809446053214</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>73637.28791628848</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>11707.658983263187</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.158990904126895</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.15899090412689504</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>24.4094563734</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.54</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>346.73685045253166</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>24.4094563734</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>346.7368504525317</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$288,A21,'Species'!$U$2:$U$288))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>8463.658024171193</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.54</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>8463.658024171193</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>1398.7218182676</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.140617594245605</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>138.23486548228146</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>1398.7218182676</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>138.58770951270054</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$288,A22,'Species'!$U$2:$U$288))</x:f>
-        <x:v>193845.65303914645</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.140617594245605</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>138.23486548228146</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>193352.12239535383</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>493.53064379261923</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0025524966453871</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.0025524966453871136</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>12521.8036905399</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.0373029257015944</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>108.96899003201995</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>12521.8036905399</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>109.54430138695982</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$288,A23,'Species'!$U$2:$U$288))</x:f>
-        <x:v>1371692.2373848485</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.0373029257015944</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>108.96899003201995</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1364488.301537353</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>7203.93584749545</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0052795878421081</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.00527958784210818</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>1.2299403008</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.502865928465558</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>318.32146762691804</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>1.2299403008</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>334.46619810713037</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$288,A24,'Species'!$U$2:$U$288))</x:f>
-        <x:v>411.3734563073163</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.502865928465558</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>318.32146762691804</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>391.516401644149</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>19.857054663167276</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.05071832132646</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.05071832132645988</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>8058.282096147799</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.7080043551200625</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>510.51011936284453</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>8058.282096147799</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>669.317051138486</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$288,A25,'Species'!$U$2:$U$288))</x:f>
-        <x:v>5393545.609835703</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.7080043551200625</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>510.51011936284453</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>4113834.554763886</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>1279711.0550718168</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.3110749929381313</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.3110749929381314</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>470.3902566379</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>4.075671028172611</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>1190.3400010012988</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>470.3902566379</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>1303.776107569693</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$288,A26,'Species'!$U$2:$U$288))</x:f>
-        <x:v>613283.5778380702</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>4.075671028172611</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>1190.3400010012988</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>559924.3385573591</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>53359.23928071116</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0952972314405744</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.09529723144057436</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>857.7060974004</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>3.82318051962082</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>665.5497423104413</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>857.7060974004</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>666.4386522069182</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$288,A27,'Species'!$U$2:$U$288))</x:f>
-        <x:v>571608.4955411783</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>3.82318051962082</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>665.5497423104413</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>570846.0721029305</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>762.4234382477589</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.001335602495151</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.00133560249515089</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab34c53211d94673"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d64605ba8eb4e02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22330,7 +20846,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -22429,7 +20945,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>466342206.932724</x:v>
+        <x:v>432788434.38743633</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -22443,7 +20959,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>466342206.9327239</x:v>
+        <x:v>451061367.4826854</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -22457,7 +20973,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-33553772.545287788</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -22471,7 +20987,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-15280839.450038731</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -22482,9 +20998,9 @@
         <x:v>EEZ_372</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -22496,47 +21012,19 @@
         <x:v>EEZ_372</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_372</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_372</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re49cb1484bd64ea4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc09c243269ce4c5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22583,7 +21071,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
